--- a/plate3d/PLATE3D_PORTAL.xlsx
+++ b/plate3d/PLATE3D_PORTAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="165">
   <si>
     <t>Portal frame shed - 18 m span, 30 m long, 6 m to eaves</t>
   </si>
@@ -479,6 +479,30 @@
   </si>
   <si>
     <t>as.gable</t>
+  </si>
+  <si>
+    <t>VIEW</t>
+  </si>
+  <si>
+    <t>ISO</t>
+  </si>
+  <si>
+    <t>PORTAL - ISOMETRIC</t>
+  </si>
+  <si>
+    <t>PLOT</t>
+  </si>
+  <si>
+    <t>PART</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>PLATES</t>
+  </si>
+  <si>
+    <t>SECTIONS</t>
   </si>
   <si>
     <t>END</t>
@@ -875,7 +899,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N116"/>
+  <dimension ref="A1:N119"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
@@ -1183,6 +1207,7 @@
         <v>7.6</v>
       </c>
     </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>22</v>
@@ -1243,6 +1268,7 @@
         <v>12000</v>
       </c>
     </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>22</v>
@@ -1429,6 +1455,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>22</v>
@@ -1489,6 +1516,7 @@
         <v>22</v>
       </c>
     </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>22</v>
@@ -1866,6 +1894,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>22</v>
@@ -2580,6 +2609,7 @@
         <v>19</v>
       </c>
     </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>22</v>
@@ -3694,6 +3724,7 @@
         <v>19</v>
       </c>
     </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>22</v>
@@ -4148,6 +4179,7 @@
         <v>19</v>
       </c>
     </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>22</v>
@@ -4338,6 +4370,7 @@
         <v>19</v>
       </c>
     </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>138</v>
@@ -4486,6 +4519,7 @@
         <v>5</v>
       </c>
     </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>22</v>
@@ -4541,6 +4575,7 @@
         <v>4</v>
       </c>
     </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>22</v>
@@ -4593,6 +4628,7 @@
         <v>6558.682558526039</v>
       </c>
     </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>22</v>
@@ -4645,16 +4681,67 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A116" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B116" s="3" t="s">
+    <row r="116" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B116" t="s">
         <v>156</v>
+      </c>
+      <c r="C116" t="s">
+        <v>149</v>
+      </c>
+      <c r="D116" t="s">
+        <v>157</v>
+      </c>
+      <c r="G116">
+        <v>50</v>
+      </c>
+      <c r="H116" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="117" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B117" t="s">
+        <v>159</v>
+      </c>
+      <c r="C117" t="s">
+        <v>160</v>
+      </c>
+      <c r="D117" t="s">
+        <v>161</v>
+      </c>
+      <c r="E117">
+        <v>10</v>
+      </c>
+      <c r="F117" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="118" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B118" t="s">
+        <v>159</v>
+      </c>
+      <c r="C118" t="s">
+        <v>15</v>
+      </c>
+      <c r="D118" t="s">
+        <v>161</v>
+      </c>
+      <c r="E118">
+        <v>20</v>
+      </c>
+      <c r="F118" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>164</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/plate3d/PLATE3D_PORTAL.xlsx
+++ b/plate3d/PLATE3D_PORTAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="157">
   <si>
     <t>Portal frame shed - 18 m span, 30 m long, 6 m to eaves</t>
   </si>
@@ -479,30 +479,6 @@
   </si>
   <si>
     <t>as.gable</t>
-  </si>
-  <si>
-    <t>VIEW</t>
-  </si>
-  <si>
-    <t>ISO</t>
-  </si>
-  <si>
-    <t>PORTAL - ISOMETRIC</t>
-  </si>
-  <si>
-    <t>PLOT</t>
-  </si>
-  <si>
-    <t>PART</t>
-  </si>
-  <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>PLATES</t>
-  </si>
-  <si>
-    <t>SECTIONS</t>
   </si>
   <si>
     <t>END</t>
@@ -899,7 +875,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N119"/>
+  <dimension ref="A1:N116"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
@@ -1207,7 +1183,6 @@
         <v>7.6</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>22</v>
@@ -1268,7 +1243,6 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>22</v>
@@ -1455,7 +1429,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>22</v>
@@ -1516,7 +1489,6 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>22</v>
@@ -1894,7 +1866,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>22</v>
@@ -2609,7 +2580,6 @@
         <v>19</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>22</v>
@@ -3724,7 +3694,6 @@
         <v>19</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>22</v>
@@ -4179,7 +4148,6 @@
         <v>19</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>22</v>
@@ -4370,7 +4338,6 @@
         <v>19</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>138</v>
@@ -4519,7 +4486,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>22</v>
@@ -4575,7 +4541,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>22</v>
@@ -4628,7 +4593,6 @@
         <v>6558.682558526039</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>22</v>
@@ -4681,67 +4645,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B116" t="s">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B116" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="C116" t="s">
-        <v>149</v>
-      </c>
-      <c r="D116" t="s">
-        <v>157</v>
-      </c>
-      <c r="G116">
-        <v>50</v>
-      </c>
-      <c r="H116" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="117" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B117" t="s">
-        <v>159</v>
-      </c>
-      <c r="C117" t="s">
-        <v>160</v>
-      </c>
-      <c r="D117" t="s">
-        <v>161</v>
-      </c>
-      <c r="E117">
-        <v>10</v>
-      </c>
-      <c r="F117" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="118" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B118" t="s">
-        <v>159</v>
-      </c>
-      <c r="C118" t="s">
-        <v>15</v>
-      </c>
-      <c r="D118" t="s">
-        <v>161</v>
-      </c>
-      <c r="E118">
-        <v>20</v>
-      </c>
-      <c r="F118" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A119" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B119" s="3" t="s">
-        <v>164</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>